--- a/tools/config-xlsx/offline.xlsx
+++ b/tools/config-xlsx/offline.xlsx
@@ -5,7 +5,6 @@
   <sheets>
     <sheet name="Global" sheetId="1" r:id="rId1"/>
     <sheet name="Levels" sheetId="2" r:id="rId2"/>
-    <sheet name="ChestWeights" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -442,7 +441,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:E3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -460,12 +459,6 @@
       <c r="E1" t="str">
         <v>expPerWin</v>
       </c>
-      <c r="F1" t="str">
-        <v>chestChance</v>
-      </c>
-      <c r="G1" t="str">
-        <v>chestGroup</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -483,12 +476,6 @@
       <c r="E2">
         <v>5</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2" t="str">
-        <v>early</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -506,104 +493,10 @@
       <c r="E3">
         <v>8</v>
       </c>
-      <c r="F3">
-        <v>0.85</v>
-      </c>
-      <c r="G3" t="str">
-        <v>early</v>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>group</v>
-      </c>
-      <c r="B1" t="str">
-        <v>type</v>
-      </c>
-      <c r="C1" t="str">
-        <v>weight</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>default</v>
-      </c>
-      <c r="B2" t="str">
-        <v>normal</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>default</v>
-      </c>
-      <c r="B3" t="str">
-        <v>boss</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>default</v>
-      </c>
-      <c r="B4" t="str">
-        <v>chapter</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>early</v>
-      </c>
-      <c r="B5" t="str">
-        <v>normal</v>
-      </c>
-      <c r="C5">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>early</v>
-      </c>
-      <c r="B6" t="str">
-        <v>boss</v>
-      </c>
-      <c r="C6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>early</v>
-      </c>
-      <c r="B7" t="str">
-        <v>chapter</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tools/config-xlsx/offline.xlsx
+++ b/tools/config-xlsx/offline.xlsx
@@ -441,7 +441,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -482,21 +482,157 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C3">
         <v>0.95</v>
       </c>
       <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>60</v>
+      </c>
+      <c r="C4">
+        <v>0.9</v>
+      </c>
+      <c r="D4">
+        <v>13</v>
+      </c>
+      <c r="E4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>75</v>
+      </c>
+      <c r="C5">
+        <v>0.85</v>
+      </c>
+      <c r="D5">
+        <v>17</v>
+      </c>
+      <c r="E5">
         <v>12</v>
       </c>
-      <c r="E3">
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>80</v>
+      </c>
+      <c r="C6">
+        <v>0.9</v>
+      </c>
+      <c r="D6">
+        <v>22</v>
+      </c>
+      <c r="E6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>90</v>
+      </c>
+      <c r="C7">
+        <v>0.88</v>
+      </c>
+      <c r="D7">
+        <v>28</v>
+      </c>
+      <c r="E7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>100</v>
+      </c>
+      <c r="C8">
+        <v>0.75</v>
+      </c>
+      <c r="D8">
+        <v>36</v>
+      </c>
+      <c r="E8">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>105</v>
+      </c>
+      <c r="C9">
+        <v>0.82</v>
+      </c>
+      <c r="D9">
+        <v>47</v>
+      </c>
+      <c r="E9">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
         <v>8</v>
+      </c>
+      <c r="B10">
+        <v>115</v>
+      </c>
+      <c r="C10">
+        <v>0.8</v>
+      </c>
+      <c r="D10">
+        <v>60</v>
+      </c>
+      <c r="E10">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>120</v>
+      </c>
+      <c r="C11">
+        <v>0.6</v>
+      </c>
+      <c r="D11">
+        <v>78</v>
+      </c>
+      <c r="E11">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E11"/>
   </ignoredErrors>
 </worksheet>
 </file>